--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0089.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0089.xlsx
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Ta không biết bọn Outcasts lại làm chuyện kinh khủng như thế... Nếu ta biết sớm hơn, có lẽ ta đã—</t>
+          <t>Tao không biết bọn Outcasts lại làm chuyện kinh khủng như thế... Nếu tao biết sớm hơn, có lẽ tao đã—</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Trong một hành động trừng phạt hiếm hoi, các Solsworn đã kết tội hắn, đuổi khỏi Rừng Bjartr, và để kẻ tội đồ lang thang nơi hoang dã.</t>
+          <t>Trong một hành động trừng phạt hiếm hoi, các Solsworn đã kết tội hắn, đuổi khỏi Bjartr Woods, và để kẻ tội đồ lang thang nơi hoang dã.</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Soliskin... Ta chỉ thấy chúng khi còn bé. Chỉ những ai có trái tim thuần khiết mới nhìn thấy được...</t>
+          <t>Soliskin... Tao chỉ thấy chúng khi còn bé. Chỉ những ai có trái tim thuần khiết mới nhìn thấy được...</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Ta không biết bọn Outcasts lại làm chuyện kinh khủng như thế... Nếu ta biết sớm hơn, có lẽ ta đã—</t>
+          <t>Tao không biết bọn Outcasts lại làm chuyện kinh khủng như thế... Nếu tao biết sớm hơn, có lẽ tao đã—</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Ta chỉ muốn biết thế giới bên ngoài Lahai-Roi trông ra sao. Ta thậm chí còn nộp đơn vào Học viện Startorch... nhưng hóa ra chẳng có gì cả.</t>
+          <t>Tao chỉ muốn biết thế giới bên ngoài Lahai-Roi trông ra sao. Tao thậm chí còn nộp đơn vào Học viện Startorch... nhưng hóa ra chẳng có gì cả.</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Ngươi đúng là đồ ngu, biết không? Ăn cắp của chính gia đình mình để chứng tỏ cái gì chứ? Về nhà đi. Và đừng bao giờ quay lại nữa.</t>
+          <t>Mày đúng là đồ ngu, biết không? Ăn cắp của chính gia đình mình để chứng tỏ cái gì chứ? Về nhà đi. Và đừng bao giờ quay lại nữa.</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Hê, ta bỏ cái đó từ lâu rồi. Ai tụ tập ở đây đều đã quyết không quay về cuộc sống của bộ tộc Roya nữa.</t>
+          <t>Hê, tao bỏ cái đó từ lâu rồi. Ai tụ tập ở đây đều đã quyết không quay về cuộc sống của bộ tộc Roya nữa.</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Hay là đến Rừng Bjartr nhờ giúp đỡ? Họ sẽ không từ chối đâu.</t>
+          <t>Hay là đến Bjartr Woods nhờ giúp đỡ? Họ sẽ không từ chối đâu.</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Hay là đến Rừng Bjartr nhờ giúp đỡ? Họ sẽ không từ chối đâu.</t>
+          <t>Hay là đến Bjartr Woods nhờ giúp đỡ? Họ sẽ không từ chối đâu.</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Nhưng trong trại không ai biết cách chữa bệnh cả, mà chúng ta cũng chẳng muốn quay lại Rừng Bjartr để cầu viện đâu...</t>
+          <t>Nhưng trong trại không ai biết cách chữa bệnh cả, mà chúng ta cũng chẳng muốn quay lại Bjartr Woods để cầu viện đâu...</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Giờ không phải lúc tỏ ra mạnh mẽ đâu. Chúng ta phải đến Rừng Bjartr.</t>
+          <t>Giờ không phải lúc tỏ ra mạnh mẽ đâu. Chúng ta phải đến Bjartr Woods.</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Cũng khá truyền cảm hứng nhỉ? Ta xứng đáng được thưởng đấy, cậu không nghĩ thế à?</t>
+          <t>Cũng khá truyền cảm hứng nhỉ? Tao xứng đáng được thưởng đấy, cậu không nghĩ thế à?</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Không có gì sâu xa đâu. Với bọn ta, đó là chuyện sinh tồn. Ngày xưa, người Roya dựa vào toán học để dự đoán khi nào thảm họa sẽ ập đến vùng băng giá.</t>
+          <t>Không có gì sâu xa đâu. Với bọn tao, đó là chuyện sinh tồn. Ngày xưa, người Roya dựa vào toán học để dự đoán khi nào thảm họa sẽ ập đến vùng băng giá.</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>...Ngươi là thằng nào mà nhiều tay thế, Chop Chop nghìn tay à?</t>
+          <t>...Mày là thằng nào mà nhiều tay thế, Chop Chop nghìn tay à?</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Nhìn đám đông này mà xem, chen chúc nhau vào cái thang máy chậm như rùa… Nếu lại trễ nữa, ta có thể nói lời tạm biệt với đống tín dụng còn lại rồi!</t>
+          <t>Nhìn đám đông này mà xem, chen chúc nhau vào cái thang máy chậm như rùa… Nếu lại trễ nữa, tao có thể nói lời tạm biệt với đống tín dụng còn lại rồi!</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Ta khá chắc là cấm bay trong khu dân cư đấy...</t>
+          <t>Tao khá chắc là cấm bay trong khu dân cư đấy...</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Ờ... Giờ ta còn chẳng biết phải làm gì nữa! Hay là quỳ xuống xin Giáo sư Wiktor tha cho...</t>
+          <t>Ờ... Giờ tao còn chẳng biết phải làm gì nữa! Hay là quỳ xuống xin Giáo sư Wiktor tha cho...</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>...Ngươi là thằng nào mà nhiều tay thế, Chop Chop nghìn tay à?</t>
+          <t>...Mày là thằng nào mà nhiều tay thế, Chop Chop nghìn tay à?</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Thật lòng mà nói, đồ này không hợp khẩu vị ta. Nhưng mấy đứa sinh viên lại mê vị mặn chát này lắm. Chúng bảo nó gợi nhớ về nhà.</t>
+          <t>Thật lòng mà nói, đồ này không hợp khẩu vị tao. Nhưng mấy đứa sinh viên lại mê vị mặn chát này lắm. Chúng bảo nó gợi nhớ về nhà.</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Này, nghe tin đồn mới ta vừa nghe này!</t>
+          <t>Này, nghe tin đồn mới tao vừa nghe này!</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Này, nghe tin đồn mới ta vừa nghe này!</t>
+          <t>Này, nghe tin đồn mới tao vừa nghe này!</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Được rồi, trước hết là dừng lại đi. Với lại gần đây ta chỉ mới cắt giảm đường thôi.</t>
+          <t>Được rồi, trước hết là dừng lại đi. Với lại gần đây tao chỉ mới cắt giảm đường thôi.</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>...Nhưng &lt;i&gt;ta&lt;/i&gt; là người hướng dẫn mà!</t>
+          <t>...Nhưng &lt;i&gt;tao&lt;/i&gt; là người hướng dẫn mà!</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Đi đi, Barry! Luận án của ta về "Liệu pháp Giải mẫn cảm Thích ứng Căng thẳng" còn trông cậy vào cậu đấy...</t>
+          <t>Đi đi, Barry! Luận án của tao về "Liệu pháp Giải mẫn cảm Thích ứng Căng thẳng" còn trông cậy vào cậu đấy...</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>"Vào lớp ngay! Bỏ học lần nữa, ta sẽ trồng &lt;i&gt;ngươi&lt;/i&gt; xuống đất để mọc lại!"</t>
+          <t>"Vào lớp ngay! Bỏ học lần nữa, tao sẽ trồng &lt;i&gt;mày&lt;/i&gt; xuống đất để mọc lại!"</t>
         </is>
       </c>
     </row>
